--- a/03_Documentos_Tecnicos/Cantidades_Pausa_Maule.xlsx
+++ b/03_Documentos_Tecnicos/Cantidades_Pausa_Maule.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\63969694-b2af-4bd1-919d-9b63abdf2687\scratchpad\pausa-maule\03_Documentos_Tecnicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\claude\C--Users-user-OneDrive-Escritorio-CURSO-BIM-IA-Claude\c32490e3-48b8-4c11-9b04-e055733501a8\scratchpad\site_repo\03_Documentos_Tecnicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E334FCD-90DD-4F18-8531-B695FA5E0344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A607F82-40A4-40E5-9D8C-A3D9797FC115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{67B9D48F-DB81-492D-9174-57B6BFBCDF5C}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{0DFC4506-5A92-49B3-AB68-C65F16549E64}"/>
   </bookViews>
   <sheets>
     <sheet name="Cantidades" sheetId="1" r:id="rId1"/>
-    <sheet name="Recintos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="102">
   <si>
     <t>Categoría</t>
   </si>
@@ -81,7 +80,7 @@
     <t>MURO_EXT_QUINCHA_12cm</t>
   </si>
   <si>
-    <t>MADERA ESTRUCTURAL, MT_TIERRA_QUINCHA</t>
+    <t>MT_MADERA ESTRUCTURAL, MT_TIERRA_QUINCHA</t>
   </si>
   <si>
     <t>No</t>
@@ -96,7 +95,7 @@
     <t>Muro cortina</t>
   </si>
   <si>
-    <t>MURO_CORTINA_EXT_MADERA</t>
+    <t>M.CORTINA_EXT_CELOSIA_PINO RADIATA (FIX N)</t>
   </si>
   <si>
     <t>Montantes de muro cortina</t>
@@ -105,7 +104,7 @@
     <t>Rectangular Mullion</t>
   </si>
   <si>
-    <t>MADERA_1.25X10cm</t>
+    <t>12.5x100mm_PINO RADIATA</t>
   </si>
   <si>
     <t>MT_PINO RADIATA</t>
@@ -114,19 +113,22 @@
     <t>Paneles de muro cortina</t>
   </si>
   <si>
+    <t>Empty System Panel</t>
+  </si>
+  <si>
     <t>Empty (celosía)</t>
   </si>
   <si>
     <t>Puertas</t>
   </si>
   <si>
-    <t>PRT_INT_SIMPLE_MADERA</t>
-  </si>
-  <si>
-    <t>80X210</t>
-  </si>
-  <si>
-    <t>M_Aluminio Grafito, TBC_Madera, TBC_Generico</t>
+    <t>PRT_Puerta_INT_Simple_1 Panel_PINO RADIATA</t>
+  </si>
+  <si>
+    <t>80x210cm</t>
+  </si>
+  <si>
+    <t>MT_PINO RADIATA PUERTA, MT_ALUMINIO GRAFITO, MT_GENERICO PUERTA</t>
   </si>
   <si>
     <t>Pilares estructurales</t>
@@ -141,31 +143,31 @@
     <t>Armazón principal</t>
   </si>
   <si>
-    <t>VIGA_Pino Radiata Dimensionada_Rectangular</t>
-  </si>
-  <si>
-    <t>2X8_PRINCIPAL</t>
+    <t>VIGA_PINO RADIATA_Rectangular</t>
+  </si>
+  <si>
+    <t>2"X8" Sin cepillar</t>
   </si>
   <si>
     <t>Armazón secundario</t>
   </si>
   <si>
-    <t>2X4_SECUNDARIA</t>
-  </si>
-  <si>
-    <t>Zapatas aisladas</t>
-  </si>
-  <si>
-    <t>Zapata</t>
-  </si>
-  <si>
-    <t>ZAPATA_Hormigon Armado_Aislada</t>
+    <t>2"X4" Cepillada</t>
+  </si>
+  <si>
+    <t>Cimentación estructural</t>
+  </si>
+  <si>
+    <t>FUNDACIÓN AISLADA</t>
+  </si>
+  <si>
+    <t>FUNDACIÓN AISLADA_HA_60x60x50cm</t>
   </si>
   <si>
     <t>MT_HORMIGON ARMADO</t>
   </si>
   <si>
-    <t>Radier estructural</t>
+    <t>Suelos</t>
   </si>
   <si>
     <t>Suelo</t>
@@ -174,37 +176,100 @@
     <t>RADIER_INT_HA_15cm</t>
   </si>
   <si>
-    <t>Radier pulido</t>
-  </si>
-  <si>
-    <t>RADIER_PULIDO_INT_HA_2cm</t>
-  </si>
-  <si>
-    <t>MT_HORMIGÓN PULIDO</t>
-  </si>
-  <si>
-    <t>Cubierta</t>
+    <t>PAV_INT_HORMIGON PULIDO_2cm</t>
+  </si>
+  <si>
+    <t>MT_HORMIGON PULIDO</t>
+  </si>
+  <si>
+    <t>Cubiertas</t>
   </si>
   <si>
     <t>Cubierta básica</t>
   </si>
   <si>
-    <t>CUBIERTA_ZINC_ONDULADO_MADERA</t>
+    <t>CUBIERTA_ZINC ONDULADO_10cm</t>
   </si>
   <si>
     <t>MT_PLANCHA ONDULADA ZINCALUM, MT_PINO RADIATA</t>
   </si>
   <si>
+    <t>Aparatos sanitarios</t>
+  </si>
+  <si>
+    <t>PLM_WC_ceramica_New Valencia a muro</t>
+  </si>
+  <si>
+    <t>41x69cm</t>
+  </si>
+  <si>
+    <t>MT_LOZA INODORO</t>
+  </si>
+  <si>
+    <t>PLM_Lavamanos_ceramica_Ciro pedestal</t>
+  </si>
+  <si>
+    <t>53x41cm</t>
+  </si>
+  <si>
+    <t>MT_LOZA LAVAMANOS</t>
+  </si>
+  <si>
+    <t>PLM_Bebedero_acero inoxidable_Wolfen sensor pie</t>
+  </si>
+  <si>
+    <t>31x32cm</t>
+  </si>
+  <si>
+    <t>MT_ACERO INOXIDABLE CEPILLADO, MT_LATON CROMADO</t>
+  </si>
+  <si>
+    <t>Mobiliario</t>
+  </si>
+  <si>
+    <t>MBL_Mueble base cocina_Lavaplatos</t>
+  </si>
+  <si>
+    <t>80x60cm</t>
+  </si>
+  <si>
+    <t>MT_ACERO INOXIDABLE</t>
+  </si>
+  <si>
+    <t>MBL_Mueble base cocina_Melamina</t>
+  </si>
+  <si>
+    <t>104x64cm</t>
+  </si>
+  <si>
+    <t>Emplazamiento</t>
+  </si>
+  <si>
+    <t>SITIO_Banca_acero galvanizado y madera</t>
+  </si>
+  <si>
+    <t>250x50cm</t>
+  </si>
+  <si>
+    <t>MT_BANCA PATAS, MT_BANCA ASIENTO</t>
+  </si>
+  <si>
+    <t>SITIO_Bicicletero_acero galvanizado_U</t>
+  </si>
+  <si>
+    <t>2 bicicletas</t>
+  </si>
+  <si>
+    <t>MT_ACERO GALVANIZADO</t>
+  </si>
+  <si>
     <t>Recintos</t>
   </si>
   <si>
     <t>9 recintos</t>
   </si>
   <si>
-    <t>Fuente: modelo Revit HAB_ARQ_MODELO_R01.rvt (02-10-2026). Pausa Maule — habitáculo ciclista, Hito 01-02.</t>
-  </si>
-  <si>
-    <t>N°</t>
+    <t>Recinto N°</t>
   </si>
   <si>
     <t>Nombre</t>
@@ -213,73 +278,73 @@
     <t>Departamento</t>
   </si>
   <si>
+    <t>Baño 1</t>
+  </si>
+  <si>
+    <t>Servicios higiénicos</t>
+  </si>
+  <si>
     <t>01</t>
   </si>
   <si>
-    <t>Baño 1</t>
-  </si>
-  <si>
-    <t>Servicios higiénicos</t>
+    <t>Baño 2</t>
   </si>
   <si>
     <t>02</t>
   </si>
   <si>
-    <t>Baño 2</t>
+    <t>Zona apoyo</t>
+  </si>
+  <si>
+    <t>Descanso y apoyo</t>
   </si>
   <si>
     <t>03</t>
   </si>
   <si>
-    <t>Zona apoyo</t>
-  </si>
-  <si>
-    <t>Descanso y apoyo</t>
+    <t>Zona de descanso 2</t>
   </si>
   <si>
     <t>04</t>
   </si>
   <si>
-    <t>Zona de descanso 2</t>
+    <t>Zona de descanso 1</t>
   </si>
   <si>
     <t>05</t>
   </si>
   <si>
-    <t>Zona de descanso 1</t>
+    <t>Estacionamiento bicicletas</t>
+  </si>
+  <si>
+    <t>Estacionamiento</t>
   </si>
   <si>
     <t>06</t>
   </si>
   <si>
-    <t>Estacionamiento bicicletas</t>
-  </si>
-  <si>
-    <t>Estacionamiento</t>
+    <t>Bebederos</t>
   </si>
   <si>
     <t>07</t>
   </si>
   <si>
-    <t>Bebederos</t>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>Patio / exterior</t>
   </si>
   <si>
     <t>08</t>
   </si>
   <si>
-    <t>Patio</t>
-  </si>
-  <si>
-    <t>Patio / exterior</t>
+    <t>Pasillo</t>
   </si>
   <si>
     <t>09</t>
   </si>
   <si>
-    <t>Pasillo</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Total recintos</t>
   </si>
 </sst>
 </file>
@@ -289,7 +354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,22 +364,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -331,12 +380,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2B2B2B"/>
+        <fgColor rgb="FFF2EFE7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -344,49 +393,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,14 +736,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4AB679-1E6A-4D5A-A303-FEADB2E91055}">
-  <dimension ref="A1:J16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA2E563-90D8-4C58-8A63-F3D35951F95D}">
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -737,28 +753,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -769,525 +785,737 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="F2" s="6">
-        <v>55.69</v>
-      </c>
-      <c r="G2" s="6">
-        <v>6.68</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="7" t="s">
+      <c r="F2" s="4">
+        <v>56.83</v>
+      </c>
+      <c r="G2" s="4">
+        <v>6.82</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>6</v>
       </c>
-      <c r="F3" s="6">
-        <v>36.68</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="F3" s="4">
+        <v>37.29</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>396</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
-        <v>0.62</v>
-      </c>
-      <c r="H4" s="6">
-        <v>246.6</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="H4" s="4">
+        <v>250.2</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5">
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
         <v>192</v>
       </c>
-      <c r="F5" s="6">
-        <v>30.51</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="F5" s="4">
+        <v>31.04</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5">
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="J6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>16</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6">
-        <v>0.64</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7" t="s">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="5">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6">
-        <v>0.71</v>
-      </c>
-      <c r="H8" s="6">
-        <v>71.2</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="I8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>16</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4">
         <v>0.24</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>48</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="5">
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10">
         <v>16</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4">
         <v>3.03</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="4"/>
+      <c r="I10" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>76.56</v>
+      </c>
+      <c r="G11" s="4">
+        <v>11.49</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="B12" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F11" s="6">
-        <v>76.56</v>
-      </c>
-      <c r="G11" s="6">
-        <v>11.49</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="F12" s="4">
+        <v>76.260000000000005</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.53</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4">
+        <v>76.53</v>
+      </c>
+      <c r="G13" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="F12" s="6">
-        <v>76.31</v>
-      </c>
-      <c r="G12" s="6">
-        <v>1.53</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6">
-        <v>76.56</v>
-      </c>
-      <c r="G13" s="6">
-        <v>7.66</v>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="J19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21">
         <v>9</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F21" s="4">
         <v>79.45</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF29015-90DD-4E68-B2CF-2CE9E0398375}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="10">
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26">
         <v>8.92</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27">
         <v>9.0399999999999991</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28">
         <v>26.34</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29">
         <v>9.16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30">
         <v>9.23</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31">
         <v>8.7799999999999994</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="10">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33">
         <v>79.45</v>
       </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/03_Documentos_Tecnicos/Cantidades_Pausa_Maule.xlsx
+++ b/03_Documentos_Tecnicos/Cantidades_Pausa_Maule.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CUBIERTA_ZINC ONDULADO_10cm</t>
+          <t>CUBIERTA_ZINC ONDULADO_18mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
